--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/59.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/59.xlsx
@@ -426,13 +426,13 @@
         <v>-17.83190623160143</v>
       </c>
       <c r="E2">
-        <v>-17.49217032545394</v>
+        <v>-16.33810683849519</v>
       </c>
       <c r="F2">
-        <v>3.09508945065269</v>
+        <v>0.6211486646394931</v>
       </c>
       <c r="G2">
-        <v>-13.58574910532759</v>
+        <v>-13.94363686264856</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.96011188470909</v>
       </c>
       <c r="E3">
-        <v>-15.91423261442922</v>
+        <v>-17.1111082946565</v>
       </c>
       <c r="F3">
-        <v>3.31317208005291</v>
+        <v>1.558128287824459</v>
       </c>
       <c r="G3">
-        <v>-13.28314500945092</v>
+        <v>-13.68728322526304</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.00036302521412</v>
       </c>
       <c r="E4">
-        <v>-16.92341663246059</v>
+        <v>-19.63392569280366</v>
       </c>
       <c r="F4">
-        <v>3.068030001072841</v>
+        <v>0.9178499875046089</v>
       </c>
       <c r="G4">
-        <v>-12.33031108080377</v>
+        <v>-13.46673919936653</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.02458882927631</v>
       </c>
       <c r="E5">
-        <v>-17.01389101465983</v>
+        <v>-19.15613545720238</v>
       </c>
       <c r="F5">
-        <v>2.518552365243456</v>
+        <v>1.402410126711402</v>
       </c>
       <c r="G5">
-        <v>-11.65548521122369</v>
+        <v>-12.82841691963527</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.03644058938127</v>
       </c>
       <c r="E6">
-        <v>-17.09312119589803</v>
+        <v>-19.00285114051675</v>
       </c>
       <c r="F6">
-        <v>2.772942337908379</v>
+        <v>1.186405042757403</v>
       </c>
       <c r="G6">
-        <v>-11.37641403637135</v>
+        <v>-12.21289912974215</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.0691662839084</v>
       </c>
       <c r="E7">
-        <v>-17.96469847425832</v>
+        <v>-20.34760866793851</v>
       </c>
       <c r="F7">
-        <v>2.855316849177567</v>
+        <v>1.231020911072184</v>
       </c>
       <c r="G7">
-        <v>-11.73510077114205</v>
+        <v>-12.21273506866418</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.14474982275065</v>
       </c>
       <c r="E8">
-        <v>-17.7790717962099</v>
+        <v>-19.63714996629713</v>
       </c>
       <c r="F8">
-        <v>1.920212649792539</v>
+        <v>1.129729801792666</v>
       </c>
       <c r="G8">
-        <v>-10.66025790002851</v>
+        <v>-11.7576132322614</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.28448229654214</v>
       </c>
       <c r="E9">
-        <v>-17.72778682807303</v>
+        <v>-19.44350788925513</v>
       </c>
       <c r="F9">
-        <v>2.536004409685636</v>
+        <v>0.8978300041137504</v>
       </c>
       <c r="G9">
-        <v>-10.54625513816716</v>
+        <v>-12.02464232399057</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.49993048541009</v>
       </c>
       <c r="E10">
-        <v>-18.86090159427231</v>
+        <v>-20.45032804385449</v>
       </c>
       <c r="F10">
-        <v>2.679258954856171</v>
+        <v>0.9394504959000087</v>
       </c>
       <c r="G10">
-        <v>-9.727219581049489</v>
+        <v>-10.64141056339106</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.803824448247521</v>
       </c>
       <c r="E11">
-        <v>-19.96123473713006</v>
+        <v>-21.22922104469978</v>
       </c>
       <c r="F11">
-        <v>2.640380359173179</v>
+        <v>0.8239098105575338</v>
       </c>
       <c r="G11">
-        <v>-9.472819911102622</v>
+        <v>-11.50681634358681</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.200634161537728</v>
       </c>
       <c r="E12">
-        <v>-21.68328660497489</v>
+        <v>-20.88134819990455</v>
       </c>
       <c r="F12">
-        <v>2.578042398642905</v>
+        <v>0.6919906449269069</v>
       </c>
       <c r="G12">
-        <v>-8.281224614460916</v>
+        <v>-10.63349297576812</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.697337799179989</v>
       </c>
       <c r="E13">
-        <v>-22.46339323685423</v>
+        <v>-23.27959633504872</v>
       </c>
       <c r="F13">
-        <v>2.69110626545101</v>
+        <v>1.621543125978372</v>
       </c>
       <c r="G13">
-        <v>-8.04082263568664</v>
+        <v>-8.223934486033011</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.312185083624273</v>
       </c>
       <c r="E14">
-        <v>-21.02610087155974</v>
+        <v>-22.97928152428205</v>
       </c>
       <c r="F14">
-        <v>3.015387252624932</v>
+        <v>1.70177216567431</v>
       </c>
       <c r="G14">
-        <v>-8.105633323928792</v>
+        <v>-9.019223842724983</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.05222860431231</v>
       </c>
       <c r="E15">
-        <v>-22.88061060412892</v>
+        <v>-23.8440525062088</v>
       </c>
       <c r="F15">
-        <v>2.938352397634189</v>
+        <v>1.834763238724159</v>
       </c>
       <c r="G15">
-        <v>-7.918669319471632</v>
+        <v>-8.831472345093557</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.920857149984036</v>
       </c>
       <c r="E16">
-        <v>-23.84962252923824</v>
+        <v>-25.3746857777494</v>
       </c>
       <c r="F16">
-        <v>3.213237836579177</v>
+        <v>2.003882727679706</v>
       </c>
       <c r="G16">
-        <v>-6.958751233477639</v>
+        <v>-7.654265204990018</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.917133255141517</v>
       </c>
       <c r="E17">
-        <v>-24.20002679100375</v>
+        <v>-26.53595406685436</v>
       </c>
       <c r="F17">
-        <v>3.125609819241435</v>
+        <v>2.080874507565504</v>
       </c>
       <c r="G17">
-        <v>-6.644282240442018</v>
+        <v>-8.616030618721977</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.030638609807488</v>
       </c>
       <c r="E18">
-        <v>-23.84382608250842</v>
+        <v>-28.32765839341116</v>
       </c>
       <c r="F18">
-        <v>3.967628716839076</v>
+        <v>1.976493587873543</v>
       </c>
       <c r="G18">
-        <v>-5.732289676545275</v>
+        <v>-7.8349489513824</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.249346699960656</v>
       </c>
       <c r="E19">
-        <v>-24.5637311809298</v>
+        <v>-28.40699725802555</v>
       </c>
       <c r="F19">
-        <v>3.688450678012781</v>
+        <v>2.006281679678214</v>
       </c>
       <c r="G19">
-        <v>-6.143692516890013</v>
+        <v>-6.62263930303592</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.564402178134824</v>
       </c>
       <c r="E20">
-        <v>-26.83257364283078</v>
+        <v>-27.6989205337122</v>
       </c>
       <c r="F20">
-        <v>3.972748027388377</v>
+        <v>2.854672379338189</v>
       </c>
       <c r="G20">
-        <v>-6.001448281066525</v>
+        <v>-6.359931580100539</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.960012006086979</v>
       </c>
       <c r="E21">
-        <v>-27.08356884317991</v>
+        <v>-29.1819097302181</v>
       </c>
       <c r="F21">
-        <v>3.894896402138474</v>
+        <v>2.452726977947396</v>
       </c>
       <c r="G21">
-        <v>-5.254261632436013</v>
+        <v>-6.608310208485825</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.415784057662899</v>
       </c>
       <c r="E22">
-        <v>-28.57076499203894</v>
+        <v>-29.8910800810043</v>
       </c>
       <c r="F22">
-        <v>4.188607318679483</v>
+        <v>2.829861118889538</v>
       </c>
       <c r="G22">
-        <v>-4.456508078352897</v>
+        <v>-6.193553959707335</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.909440409281814</v>
       </c>
       <c r="E23">
-        <v>-27.72297578764095</v>
+        <v>-30.87961199332368</v>
       </c>
       <c r="F23">
-        <v>3.767920933167754</v>
+        <v>3.953516649764984</v>
       </c>
       <c r="G23">
-        <v>-4.316153826147649</v>
+        <v>-6.650014534506368</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.41549822005015</v>
       </c>
       <c r="E24">
-        <v>-28.53068346859705</v>
+        <v>-30.43792048827454</v>
       </c>
       <c r="F24">
-        <v>4.413023645241508</v>
+        <v>2.729303943128901</v>
       </c>
       <c r="G24">
-        <v>-3.773794152143913</v>
+        <v>-6.164639835325508</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.90875213659466</v>
       </c>
       <c r="E25">
-        <v>-29.10255275170768</v>
+        <v>-31.19351675458737</v>
       </c>
       <c r="F25">
-        <v>4.383373062425703</v>
+        <v>2.944758991127441</v>
       </c>
       <c r="G25">
-        <v>-4.033506119795522</v>
+        <v>-5.990324939980008</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.37300324373939</v>
       </c>
       <c r="E26">
-        <v>-29.38951309262574</v>
+        <v>-31.63847102515904</v>
       </c>
       <c r="F26">
-        <v>4.720208785956455</v>
+        <v>3.622159748236347</v>
       </c>
       <c r="G26">
-        <v>-3.793031954146938</v>
+        <v>-5.069187611597092</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.79465219446245</v>
       </c>
       <c r="E27">
-        <v>-29.80915319349453</v>
+        <v>-31.49181186594663</v>
       </c>
       <c r="F27">
-        <v>4.511557947804509</v>
+        <v>4.143305562155184</v>
       </c>
       <c r="G27">
-        <v>-2.730460851665717</v>
+        <v>-5.018683049354119</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.16088883350312</v>
       </c>
       <c r="E28">
-        <v>-30.68681674092112</v>
+        <v>-29.63672928141548</v>
       </c>
       <c r="F28">
-        <v>5.074067459614736</v>
+        <v>3.739352198180005</v>
       </c>
       <c r="G28">
-        <v>-2.609003154421312</v>
+        <v>-5.655345030976297</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.46197320674552</v>
       </c>
       <c r="E29">
-        <v>-29.133441472914</v>
+        <v>-32.69920945553072</v>
       </c>
       <c r="F29">
-        <v>4.440447576478589</v>
+        <v>3.505997787341773</v>
       </c>
       <c r="G29">
-        <v>-3.498443882539991</v>
+        <v>-5.566112210667197</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.69096807785789</v>
       </c>
       <c r="E30">
-        <v>-29.10066890652049</v>
+        <v>-30.51865185864628</v>
       </c>
       <c r="F30">
-        <v>4.527600110927125</v>
+        <v>3.836358991252244</v>
       </c>
       <c r="G30">
-        <v>-2.828392190328904</v>
+        <v>-5.456033789790946</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.83934914455491</v>
       </c>
       <c r="E31">
-        <v>-29.35456233023454</v>
+        <v>-29.92675766347373</v>
       </c>
       <c r="F31">
-        <v>4.614104862066672</v>
+        <v>3.49733306430849</v>
       </c>
       <c r="G31">
-        <v>-3.418930040489967</v>
+        <v>-5.499700286304036</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.90827888532751</v>
       </c>
       <c r="E32">
-        <v>-29.17891188042502</v>
+        <v>-29.96451607974968</v>
       </c>
       <c r="F32">
-        <v>3.968795058142218</v>
+        <v>3.310998443987964</v>
       </c>
       <c r="G32">
-        <v>-3.249641976573536</v>
+        <v>-4.277638847482887</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.90511508451294</v>
       </c>
       <c r="E33">
-        <v>-29.99596406749595</v>
+        <v>-29.45485897255642</v>
       </c>
       <c r="F33">
-        <v>4.416499474863655</v>
+        <v>3.217354822571091</v>
       </c>
       <c r="G33">
-        <v>-4.052550329726539</v>
+        <v>-3.660746225756364</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-12.83539516123261</v>
       </c>
       <c r="E34">
-        <v>-28.94449542341797</v>
+        <v>-28.87133339735004</v>
       </c>
       <c r="F34">
-        <v>4.676774169558065</v>
+        <v>3.323689032598852</v>
       </c>
       <c r="G34">
-        <v>-3.863637279663069</v>
+        <v>-5.085823404903477</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-12.70629711481882</v>
       </c>
       <c r="E35">
-        <v>-28.8011692210752</v>
+        <v>-28.85796987055341</v>
       </c>
       <c r="F35">
-        <v>4.104542937908584</v>
+        <v>2.973234948966077</v>
       </c>
       <c r="G35">
-        <v>-3.025288452446504</v>
+        <v>-4.445712859422324</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-12.52662801736692</v>
       </c>
       <c r="E36">
-        <v>-28.45530701873938</v>
+        <v>-29.13423395586534</v>
       </c>
       <c r="F36">
-        <v>4.474268160800087</v>
+        <v>3.685685587622236</v>
       </c>
       <c r="G36">
-        <v>-3.20346534556747</v>
+        <v>-5.177891200639936</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-12.30197740322977</v>
       </c>
       <c r="E37">
-        <v>-28.69176581752389</v>
+        <v>-28.10603940394978</v>
       </c>
       <c r="F37">
-        <v>4.07725982912998</v>
+        <v>3.070619477573992</v>
       </c>
       <c r="G37">
-        <v>-4.656705249359297</v>
+        <v>-5.024300500663888</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-12.04111112305178</v>
       </c>
       <c r="E38">
-        <v>-26.60142221558325</v>
+        <v>-28.45913810774987</v>
       </c>
       <c r="F38">
-        <v>4.46519091080021</v>
+        <v>2.967930084118549</v>
       </c>
       <c r="G38">
-        <v>-3.611773993981652</v>
+        <v>-6.473291222536234</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.75935845214843</v>
       </c>
       <c r="E39">
-        <v>-28.7476788860966</v>
+        <v>-27.92179843894771</v>
       </c>
       <c r="F39">
-        <v>4.900688505473994</v>
+        <v>3.106179633441369</v>
       </c>
       <c r="G39">
-        <v>-3.751540907527759</v>
+        <v>-6.749451953865339</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.46809687623437</v>
       </c>
       <c r="E40">
-        <v>-27.06150611781455</v>
+        <v>-27.47083488336787</v>
       </c>
       <c r="F40">
-        <v>4.544931213728496</v>
+        <v>3.88239965149984</v>
       </c>
       <c r="G40">
-        <v>-4.658867574366972</v>
+        <v>-6.759292337322115</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.17592865715689</v>
       </c>
       <c r="E41">
-        <v>-26.95362428152982</v>
+        <v>-26.34156932007511</v>
       </c>
       <c r="F41">
-        <v>4.721353589707124</v>
+        <v>3.750800235686694</v>
       </c>
       <c r="G41">
-        <v>-4.997368234103966</v>
+        <v>-5.56077366318998</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.89032971925796</v>
       </c>
       <c r="E42">
-        <v>-25.66967963155706</v>
+        <v>-25.65512964457042</v>
       </c>
       <c r="F42">
-        <v>4.524828393597358</v>
+        <v>3.524148973871916</v>
       </c>
       <c r="G42">
-        <v>-4.066945048707823</v>
+        <v>-6.266465983979756</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.61538265184079</v>
       </c>
       <c r="E43">
-        <v>-25.03972814082405</v>
+        <v>-22.35088330013366</v>
       </c>
       <c r="F43">
-        <v>4.800255584823777</v>
+        <v>3.709618778623919</v>
       </c>
       <c r="G43">
-        <v>-3.481191219580431</v>
+        <v>-6.553960054575183</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.3530912920064</v>
       </c>
       <c r="E44">
-        <v>-25.68321071189198</v>
+        <v>-23.62409546670824</v>
       </c>
       <c r="F44">
-        <v>4.862774129447861</v>
+        <v>3.10378896511689</v>
       </c>
       <c r="G44">
-        <v>-4.604373046707713</v>
+        <v>-5.76688687666806</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.11070589916004</v>
       </c>
       <c r="E45">
-        <v>-24.99500493152429</v>
+        <v>-25.08215994227592</v>
       </c>
       <c r="F45">
-        <v>4.872514073369977</v>
+        <v>3.414673594652739</v>
       </c>
       <c r="G45">
-        <v>-4.794267182017458</v>
+        <v>-7.50256448863221</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.894657424359492</v>
       </c>
       <c r="E46">
-        <v>-23.31992239608703</v>
+        <v>-22.89441792137831</v>
       </c>
       <c r="F46">
-        <v>5.173887388386882</v>
+        <v>3.452659210275513</v>
       </c>
       <c r="G46">
-        <v>-4.886508882496567</v>
+        <v>-6.184442007436757</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.705845186491358</v>
       </c>
       <c r="E47">
-        <v>-23.45024282107977</v>
+        <v>-23.1836470277742</v>
       </c>
       <c r="F47">
-        <v>5.167001998534813</v>
+        <v>3.276437299208363</v>
       </c>
       <c r="G47">
-        <v>-5.699480742172387</v>
+        <v>-5.99385553437797</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.543112025773306</v>
       </c>
       <c r="E48">
-        <v>-23.20107259575572</v>
+        <v>-24.2953421119172</v>
       </c>
       <c r="F48">
-        <v>5.201405753507882</v>
+        <v>3.687845969808737</v>
       </c>
       <c r="G48">
-        <v>-5.301947625359422</v>
+        <v>-7.510678949548717</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.402798072764398</v>
       </c>
       <c r="E49">
-        <v>-22.41927684307151</v>
+        <v>-21.69324471931775</v>
       </c>
       <c r="F49">
-        <v>4.908606041109952</v>
+        <v>4.030311278208915</v>
       </c>
       <c r="G49">
-        <v>-6.371934288564987</v>
+        <v>-7.446311226217089</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.277150792293284</v>
       </c>
       <c r="E50">
-        <v>-21.27773458674396</v>
+        <v>-21.42149099411745</v>
       </c>
       <c r="F50">
-        <v>5.595779876837088</v>
+        <v>4.030153888402382</v>
       </c>
       <c r="G50">
-        <v>-5.719571661780868</v>
+        <v>-6.872917758704125</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.16221044366034</v>
       </c>
       <c r="E51">
-        <v>-21.20143432818872</v>
+        <v>-19.80977539546952</v>
       </c>
       <c r="F51">
-        <v>4.980211776142747</v>
+        <v>3.635052458493519</v>
       </c>
       <c r="G51">
-        <v>-4.116790085417348</v>
+        <v>-5.882143065165115</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.059334329851191</v>
       </c>
       <c r="E52">
-        <v>-20.04955356570166</v>
+        <v>-21.98034091445604</v>
       </c>
       <c r="F52">
-        <v>5.213940609047044</v>
+        <v>3.507346369473531</v>
       </c>
       <c r="G52">
-        <v>-6.17750878628165</v>
+        <v>-6.545038413155052</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.964811580328181</v>
       </c>
       <c r="E53">
-        <v>-21.08335889691272</v>
+        <v>-18.33546728363633</v>
       </c>
       <c r="F53">
-        <v>5.132518720291075</v>
+        <v>4.107892855685505</v>
       </c>
       <c r="G53">
-        <v>-5.83880140958641</v>
+        <v>-7.515574532115408</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.8755956131165</v>
       </c>
       <c r="E54">
-        <v>-18.43203246337589</v>
+        <v>-19.15491729769432</v>
       </c>
       <c r="F54">
-        <v>5.080999238041363</v>
+        <v>3.406038692845957</v>
       </c>
       <c r="G54">
-        <v>-5.750260927026353</v>
+        <v>-7.422427214485891</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.789670239336722</v>
       </c>
       <c r="E55">
-        <v>-18.19429663492121</v>
+        <v>-17.07340422006864</v>
       </c>
       <c r="F55">
-        <v>5.649328859223659</v>
+        <v>3.360264766902062</v>
       </c>
       <c r="G55">
-        <v>-5.200518504513867</v>
+        <v>-7.803416412196136</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.702729413622031</v>
       </c>
       <c r="E56">
-        <v>-16.85508648815885</v>
+        <v>-17.51944532440215</v>
       </c>
       <c r="F56">
-        <v>5.151475079936739</v>
+        <v>3.838249325665432</v>
       </c>
       <c r="G56">
-        <v>-6.465511446218791</v>
+        <v>-7.938113838432901</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.61420679514711</v>
       </c>
       <c r="E57">
-        <v>-18.84911850490435</v>
+        <v>-17.03427820464237</v>
       </c>
       <c r="F57">
-        <v>5.723646669133219</v>
+        <v>3.701086594375084</v>
       </c>
       <c r="G57">
-        <v>-5.948676394725975</v>
+        <v>-8.201572961105395</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.529662171561311</v>
       </c>
       <c r="E58">
-        <v>-17.10729531954204</v>
+        <v>-16.44230702541168</v>
       </c>
       <c r="F58">
-        <v>5.201816623739671</v>
+        <v>3.360902609802217</v>
       </c>
       <c r="G58">
-        <v>-6.053432674232807</v>
+        <v>-9.092769142758378</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.451303938357073</v>
       </c>
       <c r="E59">
-        <v>-16.30783398975391</v>
+        <v>-16.5954645448251</v>
       </c>
       <c r="F59">
-        <v>4.809357685845738</v>
+        <v>3.292274027215084</v>
       </c>
       <c r="G59">
-        <v>-6.5062314057715</v>
+        <v>-7.984516873726569</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.380531549580432</v>
       </c>
       <c r="E60">
-        <v>-16.43030204081735</v>
+        <v>-18.12953039966351</v>
       </c>
       <c r="F60">
-        <v>5.061444797130878</v>
+        <v>3.883178316858472</v>
       </c>
       <c r="G60">
-        <v>-5.299371866435258</v>
+        <v>-8.320116933605014</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.31880140778263</v>
       </c>
       <c r="E61">
-        <v>-15.40429474184749</v>
+        <v>-16.16433570539885</v>
       </c>
       <c r="F61">
-        <v>5.283314722296697</v>
+        <v>3.222311773109443</v>
       </c>
       <c r="G61">
-        <v>-6.119693662404234</v>
+        <v>-8.31642227812908</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.2655541796978</v>
       </c>
       <c r="E62">
-        <v>-15.93620024184043</v>
+        <v>-15.94275747220354</v>
       </c>
       <c r="F62">
-        <v>5.081989965455111</v>
+        <v>3.68661004564376</v>
       </c>
       <c r="G62">
-        <v>-5.579250221791214</v>
+        <v>-8.386591201177804</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.22001436793191</v>
       </c>
       <c r="E63">
-        <v>-15.38220031716406</v>
+        <v>-14.60975586330569</v>
       </c>
       <c r="F63">
-        <v>4.833519506250593</v>
+        <v>3.491474850035892</v>
       </c>
       <c r="G63">
-        <v>-6.51550741912005</v>
+        <v>-9.618197713515379</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.185995526681413</v>
       </c>
       <c r="E64">
-        <v>-16.11177823606583</v>
+        <v>-14.38782440913779</v>
       </c>
       <c r="F64">
-        <v>4.568970435757738</v>
+        <v>3.201196688012084</v>
       </c>
       <c r="G64">
-        <v>-6.574028005632747</v>
+        <v>-9.999925186076499</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.166353322631233</v>
       </c>
       <c r="E65">
-        <v>-14.82748036512048</v>
+        <v>-14.5562700568011</v>
       </c>
       <c r="F65">
-        <v>4.540945109786225</v>
+        <v>3.156317398863212</v>
       </c>
       <c r="G65">
-        <v>-5.797228332428245</v>
+        <v>-9.50620962169153</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.16097080189307</v>
       </c>
       <c r="E66">
-        <v>-15.91026567119851</v>
+        <v>-14.70458663750032</v>
       </c>
       <c r="F66">
-        <v>4.687718559683852</v>
+        <v>3.196453456263654</v>
       </c>
       <c r="G66">
-        <v>-5.934471986595139</v>
+        <v>-8.197031750467124</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.16932013989209</v>
       </c>
       <c r="E67">
-        <v>-14.47396051323768</v>
+        <v>-13.12219743652606</v>
       </c>
       <c r="F67">
-        <v>4.26497450954357</v>
+        <v>3.059769521332124</v>
       </c>
       <c r="G67">
-        <v>-6.44554521302957</v>
+        <v>-7.987237006399348</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.189774854650722</v>
       </c>
       <c r="E68">
-        <v>-15.72795836459771</v>
+        <v>-15.47959873612104</v>
       </c>
       <c r="F68">
-        <v>4.459675640632371</v>
+        <v>3.292111667204135</v>
       </c>
       <c r="G68">
-        <v>-5.851069896997173</v>
+        <v>-8.67037749141106</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.21826770370677</v>
       </c>
       <c r="E69">
-        <v>-16.02538400894749</v>
+        <v>-15.02608112120087</v>
       </c>
       <c r="F69">
-        <v>4.326934734538167</v>
+        <v>2.694033715852503</v>
       </c>
       <c r="G69">
-        <v>-4.985595211148679</v>
+        <v>-7.787732173141991</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.256263876997467</v>
       </c>
       <c r="E70">
-        <v>-14.52887278905469</v>
+        <v>-13.58346327047335</v>
       </c>
       <c r="F70">
-        <v>4.120545339395864</v>
+        <v>2.678303018873341</v>
       </c>
       <c r="G70">
-        <v>-5.331750960783858</v>
+        <v>-6.976627328533494</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.30810137647002</v>
       </c>
       <c r="E71">
-        <v>-13.93788428868367</v>
+        <v>-13.50165638752479</v>
       </c>
       <c r="F71">
-        <v>4.151340725962339</v>
+        <v>2.953503237431392</v>
       </c>
       <c r="G71">
-        <v>-4.749819754773219</v>
+        <v>-9.185699899764971</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.374426654201505</v>
       </c>
       <c r="E72">
-        <v>-15.57617297280862</v>
+        <v>-15.65437066197307</v>
       </c>
       <c r="F72">
-        <v>4.042836193339243</v>
+        <v>2.23837697206419</v>
       </c>
       <c r="G72">
-        <v>-4.968670670345062</v>
+        <v>-7.324978215391943</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.455668469238457</v>
       </c>
       <c r="E73">
-        <v>-14.16262792521035</v>
+        <v>-15.85657155488956</v>
       </c>
       <c r="F73">
-        <v>3.350027802538265</v>
+        <v>2.554636049309402</v>
       </c>
       <c r="G73">
-        <v>-5.369015794034472</v>
+        <v>-7.713753751862749</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.551299138997496</v>
       </c>
       <c r="E74">
-        <v>-14.83364814671892</v>
+        <v>-14.43313179158453</v>
       </c>
       <c r="F74">
-        <v>3.607996322383282</v>
+        <v>2.461978185101861</v>
       </c>
       <c r="G74">
-        <v>-4.104931750701514</v>
+        <v>-7.278155183738667</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.655238881321761</v>
       </c>
       <c r="E75">
-        <v>-14.44136455733047</v>
+        <v>-12.40303953631594</v>
       </c>
       <c r="F75">
-        <v>3.538559253211016</v>
+        <v>3.450555157072402</v>
       </c>
       <c r="G75">
-        <v>-5.239420667322643</v>
+        <v>-7.323987286480991</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.766129863832438</v>
       </c>
       <c r="E76">
-        <v>-14.56552625767278</v>
+        <v>-14.70464550766242</v>
       </c>
       <c r="F76">
-        <v>3.698793673404135</v>
+        <v>1.927899899290519</v>
       </c>
       <c r="G76">
-        <v>-5.115485647800857</v>
+        <v>-6.448340813798217</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.886362451980876</v>
       </c>
       <c r="E77">
-        <v>-14.20103844174341</v>
+        <v>-13.74934580184833</v>
       </c>
       <c r="F77">
-        <v>3.332289142974717</v>
+        <v>2.510725950021806</v>
       </c>
       <c r="G77">
-        <v>-4.989975641930537</v>
+        <v>-6.084689590808078</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.014875173259711</v>
       </c>
       <c r="E78">
-        <v>-15.25258180564252</v>
+        <v>-13.82292444752495</v>
       </c>
       <c r="F78">
-        <v>3.169377439335749</v>
+        <v>2.22447862378002</v>
       </c>
       <c r="G78">
-        <v>-4.984299128632698</v>
+        <v>-5.730947656927462</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.14991219875588</v>
       </c>
       <c r="E79">
-        <v>-16.16124275765161</v>
+        <v>-15.94345938567473</v>
       </c>
       <c r="F79">
-        <v>2.91242615466137</v>
+        <v>1.991087764776065</v>
       </c>
       <c r="G79">
-        <v>-3.506030066785427</v>
+        <v>-8.024288560248598</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.289633742074626</v>
       </c>
       <c r="E80">
-        <v>-16.86815113567098</v>
+        <v>-15.62334155807251</v>
       </c>
       <c r="F80">
-        <v>2.648558002173616</v>
+        <v>2.112986998302429</v>
       </c>
       <c r="G80">
-        <v>-2.511777278393405</v>
+        <v>-5.479356712635479</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.428963599961905</v>
       </c>
       <c r="E81">
-        <v>-17.72156470478649</v>
+        <v>-15.19779179862371</v>
       </c>
       <c r="F81">
-        <v>3.225081833704404</v>
+        <v>1.863312092894241</v>
       </c>
       <c r="G81">
-        <v>-3.979795804088971</v>
+        <v>-6.925922611775396</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.564717212069606</v>
       </c>
       <c r="E82">
-        <v>-18.90834641645067</v>
+        <v>-17.9534135170312</v>
       </c>
       <c r="F82">
-        <v>2.936281479127191</v>
+        <v>1.921710338056801</v>
       </c>
       <c r="G82">
-        <v>-3.163710065153238</v>
+        <v>-6.451251257321444</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.699645492113198</v>
       </c>
       <c r="E83">
-        <v>-19.09327570950191</v>
+        <v>-16.7192096255587</v>
       </c>
       <c r="F83">
-        <v>3.339146368335091</v>
+        <v>1.294253508397482</v>
       </c>
       <c r="G83">
-        <v>-2.486036095259561</v>
+        <v>-5.507808184777424</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.835576326471788</v>
       </c>
       <c r="E84">
-        <v>-19.87766174931851</v>
+        <v>-18.03944093775491</v>
       </c>
       <c r="F84">
-        <v>2.83834525782901</v>
+        <v>1.87673661502401</v>
       </c>
       <c r="G84">
-        <v>-3.330871897499149</v>
+        <v>-7.466024805346233</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.972972119122733</v>
       </c>
       <c r="E85">
-        <v>-20.2960067066211</v>
+        <v>-20.61814876210475</v>
       </c>
       <c r="F85">
-        <v>2.856579281099433</v>
+        <v>1.889311232198507</v>
       </c>
       <c r="G85">
-        <v>-3.311443784645677</v>
+        <v>-4.407361941835534</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.11263047655704</v>
       </c>
       <c r="E86">
-        <v>-22.26198482688909</v>
+        <v>-19.9100720377914</v>
       </c>
       <c r="F86">
-        <v>2.643231599773615</v>
+        <v>1.091480765335802</v>
       </c>
       <c r="G86">
-        <v>-2.469259209426121</v>
+        <v>-6.262531799329982</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.2539173415564</v>
       </c>
       <c r="E87">
-        <v>-21.76027972005329</v>
+        <v>-22.39510384881856</v>
       </c>
       <c r="F87">
-        <v>3.124874228987748</v>
+        <v>1.718526724763333</v>
       </c>
       <c r="G87">
-        <v>-2.44799361249936</v>
+        <v>-4.715120836782091</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.39402625784347</v>
       </c>
       <c r="E88">
-        <v>-23.8024856432924</v>
+        <v>-23.41549584001891</v>
       </c>
       <c r="F88">
-        <v>2.3736642795546</v>
+        <v>2.059790900429451</v>
       </c>
       <c r="G88">
-        <v>-3.181691159298995</v>
+        <v>-5.002112880478924</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.53757611996929</v>
       </c>
       <c r="E89">
-        <v>-24.18181779701891</v>
+        <v>-23.22449386332339</v>
       </c>
       <c r="F89">
-        <v>3.007017428387046</v>
+        <v>1.489945366900031</v>
       </c>
       <c r="G89">
-        <v>-2.16411544806244</v>
+        <v>-5.617834106108725</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.69165886811384</v>
       </c>
       <c r="E90">
-        <v>-27.77435132525797</v>
+        <v>-28.16398575735193</v>
       </c>
       <c r="F90">
-        <v>2.313496641619661</v>
+        <v>1.185051490421229</v>
       </c>
       <c r="G90">
-        <v>-2.578500918804714</v>
+        <v>-4.392652225584543</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.85851820066588</v>
       </c>
       <c r="E91">
-        <v>-28.57656596724276</v>
+        <v>-28.08071617729889</v>
       </c>
       <c r="F91">
-        <v>2.178302111278365</v>
+        <v>1.23186584582304</v>
       </c>
       <c r="G91">
-        <v>-3.518705425669562</v>
+        <v>-3.951810265408467</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-11.04102518659694</v>
       </c>
       <c r="E92">
-        <v>-30.63204484779835</v>
+        <v>-28.1188595138655</v>
       </c>
       <c r="F92">
-        <v>2.237368020567581</v>
+        <v>1.440733716234518</v>
       </c>
       <c r="G92">
-        <v>-2.288762492662626</v>
+        <v>-4.12221394465511</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-11.24126658570586</v>
       </c>
       <c r="E93">
-        <v>-30.61910473332143</v>
+        <v>-29.58013920597862</v>
       </c>
       <c r="F93">
-        <v>2.224569744194328</v>
+        <v>0.783914575615568</v>
       </c>
       <c r="G93">
-        <v>-2.038762940826974</v>
+        <v>-5.457290497648214</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.4532659983633</v>
       </c>
       <c r="E94">
-        <v>-33.66195623685043</v>
+        <v>-33.28134026074274</v>
       </c>
       <c r="F94">
-        <v>2.360544596629061</v>
+        <v>1.262086345411972</v>
       </c>
       <c r="G94">
-        <v>-2.972677345962367</v>
+        <v>-5.754204955340806</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.67877683965647</v>
       </c>
       <c r="E95">
-        <v>-34.62916356506769</v>
+        <v>-34.53752762928548</v>
       </c>
       <c r="F95">
-        <v>1.942134564740225</v>
+        <v>0.4331366003282978</v>
       </c>
       <c r="G95">
-        <v>-2.737627039551545</v>
+        <v>-4.350258843036517</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.92486736067034</v>
       </c>
       <c r="E96">
-        <v>-37.86717871290526</v>
+        <v>-37.02853249752876</v>
       </c>
       <c r="F96">
-        <v>1.40902878225977</v>
+        <v>0.1674369275129535</v>
       </c>
       <c r="G96">
-        <v>-2.144697178873647</v>
+        <v>-6.216558604060602</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.18893135869172</v>
       </c>
       <c r="E97">
-        <v>-40.24981266967098</v>
+        <v>-37.45469586520559</v>
       </c>
       <c r="F97">
-        <v>1.539004597963429</v>
+        <v>0.3957316702548861</v>
       </c>
       <c r="G97">
-        <v>-2.607444574180576</v>
+        <v>-5.34987970989979</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.47453041917092</v>
       </c>
       <c r="E98">
-        <v>-41.30657057138993</v>
+        <v>-41.92784777016125</v>
       </c>
       <c r="F98">
-        <v>0.9643180853320499</v>
+        <v>-0.351773820152943</v>
       </c>
       <c r="G98">
-        <v>-3.764498451466006</v>
+        <v>-6.165358422847026</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.77098776971579</v>
       </c>
       <c r="E99">
-        <v>-43.19521367679192</v>
+        <v>-43.1077688437038</v>
       </c>
       <c r="F99">
-        <v>0.5348344380025902</v>
+        <v>0.06583932229439976</v>
       </c>
       <c r="G99">
-        <v>-2.730556007090941</v>
+        <v>-3.908632670907734</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-13.08159309046013</v>
       </c>
       <c r="E100">
-        <v>-47.18760240296025</v>
+        <v>-45.18009817604193</v>
       </c>
       <c r="F100">
-        <v>0.950716292578082</v>
+        <v>0.04151679861340067</v>
       </c>
       <c r="G100">
-        <v>-3.423103754313581</v>
+        <v>-6.496236804901431</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.38005912295469</v>
       </c>
       <c r="E101">
-        <v>-48.42381127629965</v>
+        <v>-47.79547984714288</v>
       </c>
       <c r="F101">
-        <v>0.7637487995618168</v>
+        <v>-0.04437578901547727</v>
       </c>
       <c r="G101">
-        <v>-3.595348198855072</v>
+        <v>-8.14050942788413</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.69850722973018</v>
       </c>
       <c r="E102">
-        <v>-50.85411874318112</v>
+        <v>-49.43147259494594</v>
       </c>
       <c r="F102">
-        <v>0.5007313803967374</v>
+        <v>-0.7055919038084875</v>
       </c>
       <c r="G102">
-        <v>-4.28140568983313</v>
+        <v>-6.252212357525528</v>
       </c>
     </row>
   </sheetData>
